--- a/Prior Responses (outside data room)/Zed Portfolio Yield Analysis_20261028_v10_DRAFT.xlsx
+++ b/Prior Responses (outside data room)/Zed Portfolio Yield Analysis_20261028_v10_DRAFT.xlsx
@@ -2985,7 +2985,7 @@
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>• Fraud controls and their timing. Basic duplicate-applicant checks have been part of decisioning since May 2026, and the credit model released on 5 May 2026 (v2.1) sharply reduced uncoordinated first-payment default on new accounts: first-payment defaults fell from 1.2–1.5% of cards issued in February–April 2026 to 0.4% of cards issued in May–August. On 24 October 2026 Zed deployed a full suite of fraud-signal policies, informed by its review of first-payment defaults: bank account numbers shared across applicants, repeated selfie or ID images, invite-name mismatches, business-owner income verification and past-due bureau tradelines.</t>
+          <t>• Fraud controls and their timing. Basic duplicate-applicant checks have been part of decisioning since May 2026 and the first set of major improvements to our second generation credit model were released on 5 May 2026 (v2.1). Version 2.1 sharply reduced uncoordinated first-payment default on new accounts: first-payment defaults fell from 1.2–1.5% of cards issued in February–April 2026 to 0.4% of cards issued in May–August. On 24 October 2026 Zed deployed a full suite of fraud-signal policies, informed by its review of first-payment defaults: bank account numbers shared across applicants, repeated selfie or ID images, invite-name mismatches, business-owner income verification and past-due bureau tradelines.</t>
         </is>
       </c>
     </row>
